--- a/public/template_officer.xlsx
+++ b/public/template_officer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\TempPass-Registry\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\iocl_utility_app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A8127AC-2C58-4810-BD64-EAE3FD7C43F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F41EAB-6E17-457D-948F-FA850697C0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="255" yWindow="2490" windowWidth="21615" windowHeight="11295" xr2:uid="{28A88976-77FF-4DD6-A80E-B079E956243C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{28A88976-77FF-4DD6-A80E-B079E956243C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>LOCATION CODE</t>
   </si>
@@ -55,12 +55,15 @@
   <si>
     <t>OFFICER NAME</t>
   </si>
+  <si>
+    <t>ROLE</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -76,6 +79,11 @@
       <color rgb="FFBBBEBF"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -112,6 +120,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -470,13 +481,16 @@
       <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5"/>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
+      <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
@@ -1169,6 +1183,11 @@
       <c r="A232" s="3"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{9A491BDF-DFEE-4A14-8E1B-7606A0985EA4}">
+      <formula1>"USER,SUPER_ADMIN"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/public/template_officer.xlsx
+++ b/public/template_officer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\iocl_utility_app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74F41EAB-6E17-457D-948F-FA850697C0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F7E028-9A28-42A7-81FB-96D946F4E94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{28A88976-77FF-4DD6-A80E-B079E956243C}"/>
+    <workbookView xWindow="3855" yWindow="4695" windowWidth="21600" windowHeight="12585" xr2:uid="{28A88976-77FF-4DD6-A80E-B079E956243C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1185,7 +1185,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{9A491BDF-DFEE-4A14-8E1B-7606A0985EA4}">
-      <formula1>"USER,SUPER_ADMIN"</formula1>
+      <formula1>"SECURITY,ADMIN,SUPER_ADMIN"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
